--- a/artfynd/A 46781-2024 artfynd.xlsx
+++ b/artfynd/A 46781-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -809,6 +814,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98565620</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -946,6 +956,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98565525</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1061,6 +1076,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83524993</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525012</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1286,6 +1311,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525037</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1396,6 +1426,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525038</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525040</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1616,6 +1656,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525041</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1726,6 +1771,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525042</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1836,6 +1886,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525043</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1946,6 +2001,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525045</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2056,6 +2116,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525056</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2166,6 +2231,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525057</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2276,6 +2346,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525058</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2386,6 +2461,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525059</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2496,6 +2576,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525064</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2606,6 +2691,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525095</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2716,6 +2806,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525122</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2826,8 +2921,34 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83525126</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>